--- a/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-16,99</t>
+          <t>-4,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-36,88%</t>
+          <t>-5,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 9,54</t>
+          <t>-8,87; 10,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 15,12</t>
+          <t>-3,35; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 12,05</t>
+          <t>-6,06; 13,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 9,07</t>
+          <t>-26,95; 13,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 16,44</t>
+          <t>-13,81; 18,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 26,57</t>
+          <t>-5,15; 28,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 19,91</t>
+          <t>-9,02; 21,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 32,99</t>
+          <t>-29,08; 18,02</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 11,0</t>
+          <t>-5,74; 10,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 4,42</t>
+          <t>-10,05; 4,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 6,0</t>
+          <t>-9,49; 5,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 20,99</t>
+          <t>-11,53; 20,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 18,07</t>
+          <t>-7,94; 17,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 6,42</t>
+          <t>-13,41; 5,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 9,14</t>
+          <t>-13,32; 8,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 150,44</t>
+          <t>-14,35; 32,51</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>-12,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>-13,95%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 7,56</t>
+          <t>-9,69; 8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 7,91</t>
+          <t>-9,49; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 12,97</t>
+          <t>-4,69; 13,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 33,92</t>
+          <t>-29,95; 4,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 12,44</t>
+          <t>-14,45; 13,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 12,35</t>
+          <t>-13,56; 12,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 23,25</t>
+          <t>-7,05; 23,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 96,3</t>
+          <t>-33,19; 6,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>-2,65%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 1,35</t>
+          <t>-14,59; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 7,24</t>
+          <t>-9,69; 6,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 6,67</t>
+          <t>-10,76; 5,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 32,82</t>
+          <t>-20,44; 18,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 2,26</t>
+          <t>-21,58; 2,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 12,46</t>
+          <t>-15,01; 12,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 11,47</t>
+          <t>-15,65; 9,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 217,14</t>
+          <t>-24,18; 26,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,73</t>
+          <t>-5,75; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,46</t>
+          <t>-5,22; 3,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,43</t>
+          <t>-3,77; 4,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 16,14</t>
+          <t>-10,84; 6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,34</t>
+          <t>-8,67; 4,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,46</t>
+          <t>-7,63; 5,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 7,0</t>
+          <t>-5,66; 7,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 61,33</t>
+          <t>-13,03; 9,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 10,22</t>
+          <t>-10,37; 8,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 15,88</t>
+          <t>-3,9; 15,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 13,06</t>
+          <t>-6,75; 13,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 13,63</t>
+          <t>-24,58; 12,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 18,08</t>
+          <t>-15,24; 15,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 28,07</t>
+          <t>-5,92; 26,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 21,68</t>
+          <t>-9,9; 22,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 18,02</t>
+          <t>-26,96; 16,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 10,46</t>
+          <t>-5,87; 10,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 4,11</t>
+          <t>-9,64; 4,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 5,38</t>
+          <t>-8,9; 5,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 20,53</t>
+          <t>-11,22; 20,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 17,4</t>
+          <t>-8,35; 16,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 5,96</t>
+          <t>-12,89; 6,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 8,53</t>
+          <t>-12,58; 8,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 32,51</t>
+          <t>-14,73; 30,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 8,17</t>
+          <t>-10,2; 9,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 8,09</t>
+          <t>-9,33; 7,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 13,21</t>
+          <t>-4,52; 13,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 4,78</t>
+          <t>-32,03; 3,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 13,75</t>
+          <t>-14,91; 15,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 12,7</t>
+          <t>-13,1; 11,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 23,3</t>
+          <t>-6,91; 23,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 6,05</t>
+          <t>-34,79; 4,71</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 1,6</t>
+          <t>-15,91; 1,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 6,85</t>
+          <t>-9,14; 6,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 5,72</t>
+          <t>-11,41; 5,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 18,27</t>
+          <t>-19,49; 16,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 2,48</t>
+          <t>-23,05; 1,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 12,0</t>
+          <t>-14,41; 11,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 9,82</t>
+          <t>-16,72; 9,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 26,73</t>
+          <t>-22,99; 23,89</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,96</t>
+          <t>-5,9; 3,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,33</t>
+          <t>-4,92; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,62</t>
+          <t>-4,07; 4,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 6,87</t>
+          <t>-11,85; 6,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 4,78</t>
+          <t>-8,89; 4,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,26</t>
+          <t>-7,36; 5,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,4</t>
+          <t>-6,18; 7,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,06</t>
+          <t>-14,43; 8,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,7%</t>
+          <t>-4,26%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 8,92</t>
+          <t>-9,78; 9,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 15,35</t>
+          <t>-4,89; 15,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 13,55</t>
+          <t>-7,53; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 12,72</t>
+          <t>-23,61; 13,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 15,11</t>
+          <t>-14,67; 16,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 26,4</t>
+          <t>-7,36; 26,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 22,19</t>
+          <t>-10,54; 19,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 16,22</t>
+          <t>-25,95; 17,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 10,19</t>
+          <t>-5,91; 11,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 4,74</t>
+          <t>-10,26; 4,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,54</t>
+          <t>-9,38; 6,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 20,36</t>
+          <t>-16,03; 19,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 16,67</t>
+          <t>-8,42; 18,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 6,91</t>
+          <t>-13,51; 6,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 8,47</t>
+          <t>-12,86; 9,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 30,2</t>
+          <t>-21,4; 29,7</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-12,1</t>
+          <t>-16,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-13,95%</t>
+          <t>-18,63%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 9,46</t>
+          <t>-10,07; 7,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 7,18</t>
+          <t>-9,78; 7,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 13,05</t>
+          <t>-4,75; 12,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 3,86</t>
+          <t>-35,57; 0,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 15,73</t>
+          <t>-14,7; 12,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 11,36</t>
+          <t>-13,51; 12,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 23,64</t>
+          <t>-7,27; 23,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 4,71</t>
+          <t>-39,52; 0,97</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,65%</t>
+          <t>-2,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 1,13</t>
+          <t>-14,62; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 6,59</t>
+          <t>-9,49; 7,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 5,5</t>
+          <t>-10,13; 6,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 16,24</t>
+          <t>-19,94; 17,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 1,92</t>
+          <t>-21,09; 2,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 11,75</t>
+          <t>-14,88; 12,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 9,36</t>
+          <t>-15,04; 11,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 23,89</t>
+          <t>-23,3; 25,66</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,01%</t>
+          <t>-4,64%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,05</t>
+          <t>-5,96; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,46</t>
+          <t>-4,94; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,64</t>
+          <t>-3,55; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 6,58</t>
+          <t>-13,51; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 4,85</t>
+          <t>-9,02; 4,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 5,39</t>
+          <t>-7,28; 5,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 7,39</t>
+          <t>-5,35; 7,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 8,67</t>
+          <t>-16,1; 6,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A03-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-4,26%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.2017957562516992</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.00098748849036</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.061591259340291</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.643183844425035</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.003213279385760056</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.08069686994525285</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.04691369993254149</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.04255843560226567</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,78; 9,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,89; 15,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,53; 12,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-23,61; 13,79</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,67; 16,44</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,36; 26,57</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-10,54; 19,91</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-25,95; 17,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.777868136641683</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.88904565649833</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.531324449034969</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-23.60628071481166</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1466529926643896</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.07355494872640958</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1053895356647291</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2595355229343499</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.535097147893655</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.12268301222122</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.04787135560019</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.79474552706371</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1644166317078581</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2656695425504328</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1990989842423461</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1768302958320426</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,91</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-2,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,91; 11,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,26; 4,42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,38; 6,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-16,03; 19,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-8,42; 18,07</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 6,42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-12,86; 9,14</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-21,4; 29,7</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.795608728716359</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.907346615066941</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.572196269070236</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.218608736816941</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04311946701383502</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04030004601244519</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.02291166031970276</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.04471660642377592</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-16,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-18,63%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.907399934983318</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.25725247124352</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.378694685167879</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-16.025630670022</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.08424179811008317</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1351332774220899</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1286477335839478</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.214044666900558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,07; 7,56</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,78; 7,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,75; 12,97</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-35,57; 0,91</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-14,7; 12,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 12,35</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-7,27; 23,25</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-39,52; 0,97</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.99862189700726</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.418282768723429</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.002819440999863</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>19.50707780855912</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1807236600576445</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.06422363287080042</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.0913781565975868</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2969923069281348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-6,78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-2,58%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.6509661907349251</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.059289733282842</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.891724243465333</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-16.18561654234937</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.01009470847041085</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01571527199654822</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.06348159311149144</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1862768279464921</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-14,62; 1,35</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,49; 7,24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-10,13; 6,67</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-19,94; 17,39</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-21,09; 2,26</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-14,88; 12,46</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-15,04; 11,47</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-23,3; 25,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.06502359177746</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.779326722076284</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.749456432481617</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-35.57338023834855</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1470304448161137</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1351263635255568</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.07272753531794121</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3952158979840351</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.560687576293625</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.910314085318893</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.97185002815203</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.9058808989326537</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1244049537496566</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1234578530217604</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.2325136884350559</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.009693373458593073</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-6.778968437683764</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.376840017879521</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.281499401033416</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.01498841521569</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1044545045575908</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.02262690691680191</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.03612351418481479</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.02580034580061473</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-14.62104114703816</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-9.49478304743071</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-10.12833380867117</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-19.94134944695916</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2109423773543483</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1487850022620829</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1504383111111994</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2330081352858356</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.349036507352952</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.235270998138218</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.671700163361979</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>17.39143185261868</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02260254568608764</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1246145658660835</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1146966273626669</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2565781019068117</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,96; 2,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 3,46</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 4,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 5,25</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 4,34</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,28; 5,46</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 7,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-16,1; 6,92</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.552593652952794</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.6074659246134706</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1766449687071403</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.679345248576305</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02412439412535567</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.009228237955842399</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.00272224927411034</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.04643755485914103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.961931213498485</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.943711806169215</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.551820528158387</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.51018343728392</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.09015276919207149</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.07277263632068226</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.05353002302638124</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1609911995992762</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.730059343886936</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.458157455785055</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.433756919314734</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.252570675575955</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04341438361315633</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0546076436298123</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.06995217201249268</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.06919438222188555</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
